--- a/src/app/static/templates/deposits.xlsx
+++ b/src/app/static/templates/deposits.xlsx
@@ -17,7 +17,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="1">
+  <fonts count="3">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -25,13 +25,26 @@
       <sz val="11"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <b val="1"/>
+    </font>
+    <font>
+      <i val="1"/>
+      <color rgb="00666666"/>
+    </font>
   </fonts>
-  <fills count="2">
+  <fills count="3">
     <fill>
       <patternFill/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00E8F5E9"/>
+        <bgColor rgb="00E8F5E9"/>
+      </patternFill>
     </fill>
   </fills>
   <borders count="1">
@@ -46,8 +59,10 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="1">
+  <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -413,151 +428,246 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O2"/>
+  <dimension ref="A1:O3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="18" customWidth="1" min="1" max="1"/>
+    <col width="18" customWidth="1" min="2" max="2"/>
+    <col width="18" customWidth="1" min="3" max="3"/>
+    <col width="18" customWidth="1" min="4" max="4"/>
+    <col width="18" customWidth="1" min="5" max="5"/>
+    <col width="18" customWidth="1" min="6" max="6"/>
+    <col width="18" customWidth="1" min="7" max="7"/>
+    <col width="18" customWidth="1" min="8" max="8"/>
+    <col width="18" customWidth="1" min="9" max="9"/>
+    <col width="18" customWidth="1" min="10" max="10"/>
+    <col width="18" customWidth="1" min="11" max="11"/>
+    <col width="18" customWidth="1" min="12" max="12"/>
+    <col width="18" customWidth="1" min="13" max="13"/>
+    <col width="18" customWidth="1" min="14" max="14"/>
+    <col width="18" customWidth="1" min="15" max="15"/>
+  </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" t="inlineStr">
+      <c r="A1" s="1" t="inlineStr">
         <is>
           <t>id</t>
         </is>
       </c>
-      <c r="B1" t="inlineStr">
+      <c r="B1" s="1" t="inlineStr">
         <is>
           <t>bank_name</t>
         </is>
       </c>
-      <c r="C1" t="inlineStr">
+      <c r="C1" s="1" t="inlineStr">
         <is>
           <t>bank_color</t>
         </is>
       </c>
-      <c r="D1" t="inlineStr">
+      <c r="D1" s="1" t="inlineStr">
         <is>
           <t>bank_text_color</t>
         </is>
       </c>
-      <c r="E1" t="inlineStr">
+      <c r="E1" s="1" t="inlineStr">
         <is>
           <t>bank_abbr</t>
         </is>
       </c>
-      <c r="F1" t="inlineStr">
+      <c r="F1" s="1" t="inlineStr">
         <is>
           <t>name</t>
         </is>
       </c>
-      <c r="G1" t="inlineStr">
+      <c r="G1" s="1" t="inlineStr">
         <is>
           <t>rates</t>
         </is>
       </c>
-      <c r="H1" t="inlineStr">
+      <c r="H1" s="1" t="inlineStr">
         <is>
           <t>min_amount</t>
         </is>
       </c>
-      <c r="I1" t="inlineStr">
+      <c r="I1" s="1" t="inlineStr">
         <is>
           <t>max_amount</t>
         </is>
       </c>
-      <c r="J1" t="inlineStr">
+      <c r="J1" s="1" t="inlineStr">
         <is>
           <t>freq</t>
         </is>
       </c>
-      <c r="K1" t="inlineStr">
+      <c r="K1" s="1" t="inlineStr">
         <is>
           <t>replenishment</t>
         </is>
       </c>
-      <c r="L1" t="inlineStr">
+      <c r="L1" s="1" t="inlineStr">
         <is>
           <t>withdrawal</t>
         </is>
       </c>
-      <c r="M1" t="inlineStr">
+      <c r="M1" s="1" t="inlineStr">
         <is>
           <t>conditions</t>
         </is>
       </c>
-      <c r="N1" t="inlineStr">
+      <c r="N1" s="1" t="inlineStr">
         <is>
           <t>tags</t>
         </is>
       </c>
-      <c r="O1" t="inlineStr">
+      <c r="O1" s="1" t="inlineStr">
         <is>
           <t>is_active</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" t="inlineStr">
-        <is>
-          <t>dep_example</t>
-        </is>
-      </c>
-      <c r="B2" t="inlineStr">
+      <c r="A2" s="2" t="inlineStr">
+        <is>
+          <t>уникальный id</t>
+        </is>
+      </c>
+      <c r="B2" s="2" t="inlineStr">
+        <is>
+          <t>название банка</t>
+        </is>
+      </c>
+      <c r="C2" s="2" t="inlineStr">
+        <is>
+          <t>цвет фона HEX</t>
+        </is>
+      </c>
+      <c r="D2" s="2" t="inlineStr">
+        <is>
+          <t>цвет текста HEX</t>
+        </is>
+      </c>
+      <c r="E2" s="2" t="inlineStr">
+        <is>
+          <t>аббревиатура</t>
+        </is>
+      </c>
+      <c r="F2" s="2" t="inlineStr">
+        <is>
+          <t>название вклада</t>
+        </is>
+      </c>
+      <c r="G2" s="2" t="inlineStr">
+        <is>
+          <t>JSON {мес: ставка}</t>
+        </is>
+      </c>
+      <c r="H2" s="2" t="inlineStr">
+        <is>
+          <t>мин сумма руб</t>
+        </is>
+      </c>
+      <c r="I2" s="2" t="inlineStr">
+        <is>
+          <t>макс сумма руб</t>
+        </is>
+      </c>
+      <c r="J2" s="2" t="inlineStr">
+        <is>
+          <t>end/monthly</t>
+        </is>
+      </c>
+      <c r="K2" s="2" t="inlineStr">
+        <is>
+          <t>да/нет</t>
+        </is>
+      </c>
+      <c r="L2" s="2" t="inlineStr">
+        <is>
+          <t>да/нет</t>
+        </is>
+      </c>
+      <c r="M2" s="2" t="inlineStr">
+        <is>
+          <t>через запятую</t>
+        </is>
+      </c>
+      <c r="N2" s="2" t="inlineStr">
+        <is>
+          <t>через запятую</t>
+        </is>
+      </c>
+      <c r="O2" s="2" t="inlineStr">
+        <is>
+          <t>да/нет</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>tbank_priv</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
         <is>
           <t>Т-Банк</t>
         </is>
       </c>
-      <c r="C2" t="inlineStr">
+      <c r="C3" t="inlineStr">
         <is>
           <t>#FFDD2D</t>
         </is>
       </c>
-      <c r="D2" t="inlineStr">
+      <c r="D3" t="inlineStr">
         <is>
           <t>#000000</t>
         </is>
       </c>
-      <c r="E2" t="inlineStr">
+      <c r="E3" t="inlineStr">
         <is>
           <t>ТБ</t>
         </is>
       </c>
-      <c r="F2" t="inlineStr">
+      <c r="F3" t="inlineStr">
         <is>
           <t>Т-Привилегия</t>
         </is>
       </c>
-      <c r="G2" t="inlineStr">
+      <c r="G3" t="inlineStr">
         <is>
           <t>{"3": "22.5", "6": "21", "12": "19"}</t>
         </is>
       </c>
-      <c r="H2" t="n">
+      <c r="H3" t="n">
         <v>50000</v>
       </c>
-      <c r="J2" t="inlineStr">
+      <c r="I3" t="inlineStr"/>
+      <c r="J3" t="inlineStr">
         <is>
           <t>end</t>
         </is>
       </c>
-      <c r="K2" t="inlineStr">
+      <c r="K3" t="inlineStr">
         <is>
           <t>нет</t>
         </is>
       </c>
-      <c r="L2" t="inlineStr">
+      <c r="L3" t="inlineStr">
         <is>
           <t>нет</t>
         </is>
       </c>
-      <c r="M2" t="inlineStr">
-        <is>
-          <t>премиальный клиент</t>
-        </is>
-      </c>
-      <c r="N2" t="inlineStr">
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>премиальный</t>
+        </is>
+      </c>
+      <c r="N3" t="inlineStr">
         <is>
           <t>вклад</t>
         </is>
       </c>
-      <c r="O2" t="inlineStr">
+      <c r="O3" t="inlineStr">
         <is>
           <t>да</t>
         </is>
